--- a/02_DIA_inicio_2026_analisis_assets/rbd_9592_escuela-basica-sendero-del-saber_nt2_rubricas.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9592_escuela-basica-sendero-del-saber_nt2_rubricas.xlsx
@@ -1872,13 +1872,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1D32D372-2014-4A5F-BB4A-79544C88C28A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6E69EC73-D840-49FB-8EEE-0CABDD093EFB}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8BF48CC9-E895-42DC-9CF1-372C2FAFCF65}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8282A283-C72F-4E35-9C90-75EC599A276E}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FF76564C-902A-4183-BF47-DEB7F5AAA137}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E05A38D4-D966-42BF-9FA2-966CFF66FEC5}"/>
 </file>